--- a/aetherion/Settings/Aetherion_Settings.xlsx
+++ b/aetherion/Settings/Aetherion_Settings.xlsx
@@ -846,7 +846,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>الإصدار 1.1.0   ·   24 أغسطس 2026   ·   متوافق مع MT5 Build 4000+</t>
+          <t>الإصدار 1.2.0   ·   24 أغسطس 2026   ·   متوافق مع MT5 Build 4000+</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -1346,7 +1346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q105"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2094,2487 +2094,2487 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>STRATEGY</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>InpPullback</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>دخول الاتجاه عند ارتداد EMA</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Trend entry only on EMA pullback</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>STRATEGY</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>InpAllowBuy</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="15" t="inlineStr">
+      <c r="D13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P12" s="15" t="inlineStr">
+      <c r="P13" s="15" t="inlineStr">
         <is>
           <t>السماح بالشراء</t>
         </is>
       </c>
-      <c r="Q12" s="15" t="inlineStr">
+      <c r="Q13" s="15" t="inlineStr">
         <is>
           <t>Allow BUY</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>STRATEGY</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>InpAllowSell</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="D14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>السماح بالبيع</t>
         </is>
       </c>
-      <c r="Q13" s="11" t="inlineStr">
+      <c r="Q14" s="11" t="inlineStr">
         <is>
           <t>Allow SELL</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>STRATEGY</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>InpCloseOnOpposite</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="D15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="P15" s="15" t="inlineStr">
         <is>
           <t>إغلاق الصفقة عند الإشارة المعاكسة</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="Q15" s="15" t="inlineStr">
         <is>
           <t>Close on opposite signal</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>STRATEGY</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>InpOneDirection</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="D16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P16" s="11" t="inlineStr">
         <is>
           <t>اتجاه واحد لكل رمز</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q16" s="11" t="inlineStr">
         <is>
           <t>One direction per symbol</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>EMA</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>InpUseEMA</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="15" t="inlineStr">
+      <c r="D17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P16" s="15" t="inlineStr">
+      <c r="P17" s="15" t="inlineStr">
         <is>
           <t>تفعيل فلتر المتوسطات</t>
         </is>
       </c>
-      <c r="Q16" s="15" t="inlineStr">
+      <c r="Q17" s="15" t="inlineStr">
         <is>
           <t>Enable EMA filter</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>EMA</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>InpEMAFast</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D18" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E18" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F18" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G18" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H18" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I18" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J18" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K18" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L18" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M18" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="N17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="N18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="P18" s="11" t="inlineStr">
         <is>
           <t>المتوسط السريع</t>
         </is>
       </c>
-      <c r="Q17" s="11" t="inlineStr">
+      <c r="Q18" s="11" t="inlineStr">
         <is>
           <t>Fast EMA</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>EMA</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>InpEMASlow</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D19" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E19" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F19" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G19" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H19" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="I18" s="15" t="n">
+      <c r="I19" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J19" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="K18" s="15" t="n">
+      <c r="K19" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="L18" s="15" t="n">
+      <c r="L19" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="M18" s="15" t="n">
+      <c r="M19" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="N18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="15" t="inlineStr">
+      <c r="N19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P18" s="15" t="inlineStr">
+      <c r="P19" s="15" t="inlineStr">
         <is>
           <t>المتوسط البطيء</t>
         </is>
       </c>
-      <c r="Q18" s="15" t="inlineStr">
+      <c r="Q19" s="15" t="inlineStr">
         <is>
           <t>Slow EMA</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>EMA</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>InpEMATrend</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D20" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E20" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F20" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G20" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H20" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I20" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J20" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K20" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L20" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M20" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="N19" s="11" t="n">
+      <c r="N20" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="O19" s="11" t="inlineStr">
+      <c r="O20" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P19" s="11" t="inlineStr">
+      <c r="P20" s="11" t="inlineStr">
         <is>
           <t>متوسط الاتجاه العام</t>
         </is>
       </c>
-      <c r="Q19" s="11" t="inlineStr">
+      <c r="Q20" s="11" t="inlineStr">
         <is>
           <t>Higher-timeframe trend EMA</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>InpUseRSI</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" s="15" t="inlineStr">
+      <c r="D21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P20" s="15" t="inlineStr">
+      <c r="P21" s="15" t="inlineStr">
         <is>
           <t>تفعيل RSI</t>
         </is>
       </c>
-      <c r="Q20" s="15" t="inlineStr">
+      <c r="Q21" s="15" t="inlineStr">
         <is>
           <t>Enable RSI</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>InpRSIPeriod</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E22" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F22" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G22" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H22" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I22" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J22" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K22" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L22" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M22" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="N22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P22" s="11" t="inlineStr">
         <is>
           <t>فترة RSI</t>
         </is>
       </c>
-      <c r="Q21" s="11" t="inlineStr">
+      <c r="Q22" s="11" t="inlineStr">
         <is>
           <t>RSI period</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>InpRSIBuyMin</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D23" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="E22" s="15" t="n">
+      <c r="E23" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F23" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G23" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H23" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="I22" s="15" t="n">
+      <c r="I23" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J23" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="K22" s="15" t="n">
+      <c r="K23" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="L22" s="15" t="n">
+      <c r="L23" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="M22" s="15" t="n">
+      <c r="M23" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="N22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="15" t="inlineStr">
+      <c r="N23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P22" s="15" t="inlineStr">
+      <c r="P23" s="15" t="inlineStr">
         <is>
           <t>حد RSI الأدنى للشراء الاتجاهي</t>
         </is>
       </c>
-      <c r="Q22" s="15" t="inlineStr">
+      <c r="Q23" s="15" t="inlineStr">
         <is>
           <t>Trend BUY RSI floor</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>InpRSIBuyMax</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D24" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E24" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F24" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G24" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="H24" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="I24" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J24" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K24" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L24" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="M23" s="11" t="n">
+      <c r="M24" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="N23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" s="11" t="inlineStr">
+      <c r="N24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P23" s="11" t="inlineStr">
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>حد RSI الأعلى للشراء الاتجاهي</t>
         </is>
       </c>
-      <c r="Q23" s="11" t="inlineStr">
+      <c r="Q24" s="11" t="inlineStr">
         <is>
           <t>Trend BUY RSI ceiling</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>InpRSISellMin</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D25" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="E24" s="15" t="n">
+      <c r="E25" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="F24" s="15" t="n">
+      <c r="F25" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G25" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="H25" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="I24" s="15" t="n">
+      <c r="I25" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J25" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="K24" s="15" t="n">
+      <c r="K25" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="L24" s="15" t="n">
+      <c r="L25" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="M24" s="15" t="n">
+      <c r="M25" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="N24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" s="15" t="inlineStr">
+      <c r="N25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P24" s="15" t="inlineStr">
+      <c r="P25" s="15" t="inlineStr">
         <is>
           <t>حد RSI الأدنى للبيع الاتجاهي</t>
         </is>
       </c>
-      <c r="Q24" s="15" t="inlineStr">
+      <c r="Q25" s="15" t="inlineStr">
         <is>
           <t>Trend SELL RSI floor</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>InpRSISellMax</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D26" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E26" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F26" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G26" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="H26" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I26" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J26" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="K26" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L26" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="M25" s="11" t="n">
+      <c r="M26" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="N25" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="11" t="inlineStr">
+      <c r="N26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P25" s="11" t="inlineStr">
+      <c r="P26" s="11" t="inlineStr">
         <is>
           <t>حد RSI الأعلى للبيع الاتجاهي</t>
         </is>
       </c>
-      <c r="Q25" s="11" t="inlineStr">
+      <c r="Q26" s="11" t="inlineStr">
         <is>
           <t>Trend SELL RSI ceiling</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>InpRSIRangeLow</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D27" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="E27" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="F26" s="15" t="n">
+      <c r="F27" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G27" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="H26" s="15" t="n">
+      <c r="H27" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="I26" s="15" t="n">
+      <c r="I27" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J27" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="K26" s="15" t="n">
+      <c r="K27" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="L26" s="15" t="n">
+      <c r="L27" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="M26" s="15" t="n">
+      <c r="M27" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="N26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" s="15" t="inlineStr">
+      <c r="N27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P26" s="15" t="inlineStr">
+      <c r="P27" s="15" t="inlineStr">
         <is>
           <t>تشبع بيعي للنطاق</t>
         </is>
       </c>
-      <c r="Q26" s="15" t="inlineStr">
+      <c r="Q27" s="15" t="inlineStr">
         <is>
           <t>Range oversold</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>InpRSIRangeHigh</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D28" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E28" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F28" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G28" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="H27" s="11" t="n">
+      <c r="H28" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="I27" s="11" t="n">
+      <c r="I28" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J28" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="K28" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L28" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="M27" s="11" t="n">
+      <c r="M28" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="N27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" s="11" t="inlineStr">
+      <c r="N28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="P28" s="11" t="inlineStr">
         <is>
           <t>تشبع شرائي للنطاق</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="inlineStr">
+      <c r="Q28" s="11" t="inlineStr">
         <is>
           <t>Range overbought</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>InpUseMACD</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" s="15" t="inlineStr">
+      <c r="D29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P28" s="15" t="inlineStr">
+      <c r="P29" s="15" t="inlineStr">
         <is>
           <t>تفعيل MACD</t>
         </is>
       </c>
-      <c r="Q28" s="15" t="inlineStr">
+      <c r="Q29" s="15" t="inlineStr">
         <is>
           <t>Enable MACD</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>InpMACDFast</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D30" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E30" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F30" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G30" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H30" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="I29" s="11" t="n">
+      <c r="I30" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="J30" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="K29" s="11" t="n">
+      <c r="K30" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="L29" s="11" t="n">
+      <c r="L30" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M29" s="11" t="n">
+      <c r="M30" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="N29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="11" t="inlineStr">
+      <c r="N30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P29" s="11" t="inlineStr">
+      <c r="P30" s="11" t="inlineStr">
         <is>
           <t>MACD السريع</t>
         </is>
       </c>
-      <c r="Q29" s="11" t="inlineStr">
+      <c r="Q30" s="11" t="inlineStr">
         <is>
           <t>MACD fast</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>InpMACDSlow</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D31" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="E30" s="15" t="n">
+      <c r="E31" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="F30" s="15" t="n">
+      <c r="F31" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="G30" s="15" t="n">
+      <c r="G31" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="H30" s="15" t="n">
+      <c r="H31" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="I30" s="15" t="n">
+      <c r="I31" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J31" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="K30" s="15" t="n">
+      <c r="K31" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="L30" s="15" t="n">
+      <c r="L31" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="M30" s="15" t="n">
+      <c r="M31" s="15" t="n">
         <v>52</v>
       </c>
-      <c r="N30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="15" t="inlineStr">
+      <c r="N31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P30" s="15" t="inlineStr">
+      <c r="P31" s="15" t="inlineStr">
         <is>
           <t>MACD البطيء</t>
         </is>
       </c>
-      <c r="Q30" s="15" t="inlineStr">
+      <c r="Q31" s="15" t="inlineStr">
         <is>
           <t>MACD slow</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>InpMACDSignal</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D32" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E32" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F32" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G32" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="H31" s="11" t="n">
+      <c r="H32" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="I31" s="11" t="n">
+      <c r="I32" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J32" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="K31" s="11" t="n">
+      <c r="K32" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="L31" s="11" t="n">
+      <c r="L32" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M31" s="11" t="n">
+      <c r="M32" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="N31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="11" t="inlineStr">
+      <c r="N32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P31" s="11" t="inlineStr">
+      <c r="P32" s="11" t="inlineStr">
         <is>
           <t>خط إشارة MACD</t>
         </is>
       </c>
-      <c r="Q31" s="11" t="inlineStr">
+      <c r="Q32" s="11" t="inlineStr">
         <is>
           <t>MACD signal</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>ADX</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>InpUseADX</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="15" t="inlineStr">
+      <c r="D33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P32" s="15" t="inlineStr">
+      <c r="P33" s="15" t="inlineStr">
         <is>
           <t>تفعيل نظام ADX</t>
         </is>
       </c>
-      <c r="Q32" s="15" t="inlineStr">
+      <c r="Q33" s="15" t="inlineStr">
         <is>
           <t>Enable ADX regime</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>ADX</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>InpADXPeriod</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D34" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E34" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F34" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G34" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="11" t="n">
+      <c r="H34" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="I33" s="11" t="n">
+      <c r="I34" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="J33" s="11" t="n">
+      <c r="J34" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="K33" s="11" t="n">
+      <c r="K34" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L34" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M33" s="11" t="n">
+      <c r="M34" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="11" t="inlineStr">
+      <c r="N34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P33" s="11" t="inlineStr">
+      <c r="P34" s="11" t="inlineStr">
         <is>
           <t>فترة ADX</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="inlineStr">
+      <c r="Q34" s="11" t="inlineStr">
         <is>
           <t>ADX period</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>ADX</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>InpADXMin</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D35" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="E34" s="15" t="n">
+      <c r="E35" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="F34" s="15" t="n">
+      <c r="F35" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G35" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="H34" s="15" t="n">
+      <c r="H35" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="I34" s="15" t="n">
+      <c r="I35" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J35" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="K34" s="15" t="n">
+      <c r="K35" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="L34" s="15" t="n">
+      <c r="L35" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="M34" s="15" t="n">
+      <c r="M35" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="N34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" s="15" t="inlineStr">
+      <c r="N35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P34" s="15" t="inlineStr">
+      <c r="P35" s="15" t="inlineStr">
         <is>
           <t>أدنى ADX للتداول الاتجاهي</t>
         </is>
       </c>
-      <c r="Q34" s="15" t="inlineStr">
+      <c r="Q35" s="15" t="inlineStr">
         <is>
           <t>Minimum ADX to trade trend</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>ADX</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>InpADXTrend</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D36" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E36" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F36" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G36" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="H35" s="11" t="n">
+      <c r="H36" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="I36" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="J35" s="11" t="n">
+      <c r="J36" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="K35" s="11" t="n">
+      <c r="K36" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L36" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="M36" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" s="11" t="inlineStr">
+      <c r="N36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P35" s="11" t="inlineStr">
+      <c r="P36" s="11" t="inlineStr">
         <is>
           <t>ADX للاتجاه القوي</t>
         </is>
       </c>
-      <c r="Q35" s="11" t="inlineStr">
+      <c r="Q36" s="11" t="inlineStr">
         <is>
           <t>Strong-trend ADX</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>InpUseBB</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" s="15" t="inlineStr">
+      <c r="D37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P36" s="15" t="inlineStr">
+      <c r="P37" s="15" t="inlineStr">
         <is>
           <t>تفعيل بولينجر</t>
         </is>
       </c>
-      <c r="Q36" s="15" t="inlineStr">
+      <c r="Q37" s="15" t="inlineStr">
         <is>
           <t>Enable Bollinger</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>InpBBPeriod</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D38" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G38" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="H37" s="11" t="n">
+      <c r="H38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="I37" s="11" t="n">
+      <c r="I38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="J38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="K38" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="L37" s="11" t="n">
+      <c r="L38" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="M37" s="11" t="n">
+      <c r="M38" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N37" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" s="11" t="inlineStr">
+      <c r="N38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P37" s="11" t="inlineStr">
+      <c r="P38" s="11" t="inlineStr">
         <is>
           <t>فترة بولينجر</t>
         </is>
       </c>
-      <c r="Q37" s="11" t="inlineStr">
+      <c r="Q38" s="11" t="inlineStr">
         <is>
           <t>BB period</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>BB</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>InpBBDev</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="15" t="n">
+      <c r="E39" s="15" t="n">
         <v>2.2</v>
       </c>
-      <c r="F38" s="15" t="n">
+      <c r="F39" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G39" s="15" t="n">
         <v>1.8</v>
       </c>
-      <c r="H38" s="15" t="n">
+      <c r="H39" s="15" t="n">
         <v>2.2</v>
       </c>
-      <c r="I38" s="15" t="n">
+      <c r="I39" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="15" t="n">
+      <c r="J39" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="15" t="n">
+      <c r="K39" s="15" t="n">
         <v>1.8</v>
       </c>
-      <c r="L38" s="15" t="n">
+      <c r="L39" s="15" t="n">
         <v>1.2</v>
       </c>
-      <c r="M38" s="15" t="n">
+      <c r="M39" s="15" t="n">
         <v>3.2</v>
       </c>
-      <c r="N38" s="15" t="n">
+      <c r="N39" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="O38" s="15" t="inlineStr">
+      <c r="O39" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P38" s="15" t="inlineStr">
+      <c r="P39" s="15" t="inlineStr">
         <is>
           <t>انحراف بولينجر</t>
         </is>
       </c>
-      <c r="Q38" s="15" t="inlineStr">
+      <c r="Q39" s="15" t="inlineStr">
         <is>
           <t>BB deviation</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>InpATRPeriod</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D40" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E40" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F40" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G40" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="H39" s="11" t="n">
+      <c r="H40" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="I39" s="11" t="n">
+      <c r="I40" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="J40" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="K39" s="11" t="n">
+      <c r="K40" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="L39" s="11" t="n">
+      <c r="L40" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="M39" s="11" t="n">
+      <c r="M40" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" s="11" t="inlineStr">
+      <c r="N40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P39" s="11" t="inlineStr">
+      <c r="P40" s="11" t="inlineStr">
         <is>
           <t>فترة ATR</t>
         </is>
       </c>
-      <c r="Q39" s="11" t="inlineStr">
+      <c r="Q40" s="11" t="inlineStr">
         <is>
           <t>ATR period</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>InpATRSL</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D41" s="12" t="n">
         <v>1.8</v>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="E41" s="15" t="n">
         <v>2.4</v>
       </c>
-      <c r="F40" s="15" t="n">
+      <c r="F41" s="15" t="n">
         <v>1.8</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G41" s="15" t="n">
         <v>1.4</v>
       </c>
-      <c r="H40" s="15" t="n">
+      <c r="H41" s="15" t="n">
         <v>2.4</v>
       </c>
-      <c r="I40" s="15" t="n">
+      <c r="I41" s="15" t="n">
         <v>1.8</v>
       </c>
-      <c r="J40" s="15" t="n">
+      <c r="J41" s="15" t="n">
         <v>2.2</v>
       </c>
-      <c r="K40" s="15" t="n">
+      <c r="K41" s="15" t="n">
         <v>1.2</v>
       </c>
-      <c r="L40" s="15" t="n">
+      <c r="L41" s="15" t="n">
         <v>0.8</v>
       </c>
-      <c r="M40" s="15" t="n">
+      <c r="M41" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="N40" s="15" t="n">
+      <c r="N41" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="O40" s="15" t="inlineStr">
+      <c r="O41" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P40" s="15" t="inlineStr">
+      <c r="P41" s="15" t="inlineStr">
         <is>
           <t>وقف الخسارة = ATR ×</t>
         </is>
       </c>
-      <c r="Q40" s="15" t="inlineStr">
+      <c r="Q41" s="15" t="inlineStr">
         <is>
           <t>Stop-loss = ATR ×</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>InpATRTP</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D42" s="12" t="n">
         <v>2.8</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E42" s="11" t="n">
         <v>3.2</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F42" s="11" t="n">
         <v>2.8</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G42" s="11" t="n">
         <v>2.2</v>
       </c>
-      <c r="H41" s="11" t="n">
+      <c r="H42" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="I41" s="11" t="n">
+      <c r="I42" s="11" t="n">
         <v>2.8</v>
       </c>
-      <c r="J41" s="11" t="n">
+      <c r="J42" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K41" s="11" t="n">
+      <c r="K42" s="11" t="n">
         <v>1.8</v>
       </c>
-      <c r="L41" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" s="11" t="n">
+      <c r="L42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="N41" s="11" t="n">
+      <c r="N42" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="O41" s="11" t="inlineStr">
+      <c r="O42" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P41" s="11" t="inlineStr">
+      <c r="P42" s="11" t="inlineStr">
         <is>
           <t>جني الربح = ATR ×</t>
         </is>
       </c>
-      <c r="Q41" s="11" t="inlineStr">
+      <c r="Q42" s="11" t="inlineStr">
         <is>
           <t>Take-profit = ATR ×</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>InpATRTrail</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D43" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="E42" s="15" t="n">
+      <c r="E43" s="15" t="n">
         <v>1.6</v>
       </c>
-      <c r="F42" s="15" t="n">
+      <c r="F43" s="15" t="n">
         <v>1.2</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G43" s="15" t="n">
         <v>0.9</v>
       </c>
-      <c r="H42" s="15" t="n">
+      <c r="H43" s="15" t="n">
         <v>1.5</v>
       </c>
-      <c r="I42" s="15" t="n">
+      <c r="I43" s="15" t="n">
         <v>1.2</v>
       </c>
-      <c r="J42" s="15" t="n">
+      <c r="J43" s="15" t="n">
         <v>1.4</v>
       </c>
-      <c r="K42" s="15" t="n">
+      <c r="K43" s="15" t="n">
         <v>0.8</v>
       </c>
-      <c r="L42" s="15" t="n">
+      <c r="L43" s="15" t="n">
         <v>0.4</v>
       </c>
-      <c r="M42" s="15" t="n">
+      <c r="M43" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="N42" s="15" t="n">
+      <c r="N43" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="O42" s="15" t="inlineStr">
+      <c r="O43" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P42" s="15" t="inlineStr">
+      <c r="P43" s="15" t="inlineStr">
         <is>
           <t>المتحرك = ATR ×</t>
         </is>
       </c>
-      <c r="Q42" s="15" t="inlineStr">
+      <c r="Q43" s="15" t="inlineStr">
         <is>
           <t>Trailing distance = ATR ×</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>InpMinATRPoints</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="11" t="n">
+      <c r="D44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="N43" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" s="11" t="inlineStr">
+      <c r="N44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P43" s="11" t="inlineStr">
+      <c r="P44" s="11" t="inlineStr">
         <is>
           <t>أدنى ATR بالنقاط (0=إيقاف)</t>
         </is>
       </c>
-      <c r="Q43" s="11" t="inlineStr">
+      <c r="Q44" s="11" t="inlineStr">
         <is>
           <t>Min ATR in points (0=off)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>ATR</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>InpMaxATRPoints</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="15" t="n">
+      <c r="D45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="15" t="n">
         <v>20000</v>
       </c>
-      <c r="N44" s="15" t="n">
+      <c r="N45" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="O44" s="15" t="inlineStr">
+      <c r="O45" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P44" s="15" t="inlineStr">
+      <c r="P45" s="15" t="inlineStr">
         <is>
           <t>أقصى ATR بالنقاط (0=إيقاف)</t>
         </is>
       </c>
-      <c r="Q44" s="15" t="inlineStr">
+      <c r="Q45" s="15" t="inlineStr">
         <is>
           <t>Max ATR in points (0=off)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>InpLotMode</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="11" t="n">
+      <c r="D46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="N45" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" s="11" t="inlineStr">
+      <c r="N46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P45" s="11" t="inlineStr">
+      <c r="P46" s="11" t="inlineStr">
         <is>
           <t>0 ثابت 1 نسبة مخاطرة 2 خطوة رصيد</t>
         </is>
       </c>
-      <c r="Q45" s="11" t="inlineStr">
+      <c r="Q46" s="11" t="inlineStr">
         <is>
           <t>0 Fixed 1 Risk% 2 Equity step</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>InpFixedLot</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D47" s="12" t="n">
         <v>0.01</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="E47" s="15" t="n">
         <v>0.01</v>
       </c>
-      <c r="F46" s="15" t="n">
+      <c r="F47" s="15" t="n">
         <v>0.01</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G47" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H47" s="15" t="n">
         <v>0.01</v>
       </c>
-      <c r="I46" s="15" t="n">
+      <c r="I47" s="15" t="n">
         <v>0.01</v>
       </c>
-      <c r="J46" s="15" t="n">
+      <c r="J47" s="15" t="n">
         <v>0.01</v>
       </c>
-      <c r="K46" s="15" t="n">
+      <c r="K47" s="15" t="n">
         <v>0.02</v>
       </c>
-      <c r="L46" s="15" t="n">
+      <c r="L47" s="15" t="n">
         <v>0.01</v>
       </c>
-      <c r="M46" s="15" t="n">
+      <c r="M47" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="N46" s="15" t="n">
+      <c r="N47" s="15" t="n">
         <v>0.01</v>
       </c>
-      <c r="O46" s="15" t="inlineStr">
+      <c r="O47" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P46" s="15" t="inlineStr">
+      <c r="P47" s="15" t="inlineStr">
         <is>
           <t>لوت ثابت</t>
         </is>
       </c>
-      <c r="Q46" s="15" t="inlineStr">
+      <c r="Q47" s="15" t="inlineStr">
         <is>
           <t>Fixed lot</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>InpRiskPercent</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D48" s="12" t="n">
         <v>0.75</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E48" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="F48" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="G47" s="11" t="n">
+      <c r="G48" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="H47" s="11" t="n">
+      <c r="H48" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="I47" s="11" t="n">
+      <c r="I48" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="J47" s="11" t="n">
+      <c r="J48" s="11" t="n">
         <v>0.6</v>
       </c>
-      <c r="K47" s="11" t="n">
+      <c r="K48" s="11" t="n">
         <v>0.35</v>
       </c>
-      <c r="L47" s="11" t="n">
+      <c r="L48" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="M47" s="11" t="n">
+      <c r="M48" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="N47" s="11" t="n">
+      <c r="N48" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="O47" s="11" t="inlineStr">
+      <c r="O48" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P47" s="11" t="inlineStr">
+      <c r="P48" s="11" t="inlineStr">
         <is>
           <t>نسبة المخاطرة من حقوق الملكية</t>
         </is>
       </c>
-      <c r="Q47" s="11" t="inlineStr">
+      <c r="Q48" s="11" t="inlineStr">
         <is>
           <t>Risk percent of equity</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>InpEquityStep</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D49" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="E48" s="15" t="n">
+      <c r="E49" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="F48" s="15" t="n">
+      <c r="F49" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G49" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="H48" s="15" t="n">
+      <c r="H49" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="I48" s="15" t="n">
+      <c r="I49" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="J48" s="15" t="n">
+      <c r="J49" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="K48" s="15" t="n">
+      <c r="K49" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="L48" s="15" t="n">
+      <c r="L49" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="M48" s="15" t="n">
+      <c r="M49" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="N48" s="15" t="n">
+      <c r="N49" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="O48" s="15" t="inlineStr">
+      <c r="O49" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P48" s="15" t="inlineStr">
+      <c r="P49" s="15" t="inlineStr">
         <is>
           <t>خطوة الرصيد</t>
         </is>
       </c>
-      <c r="Q48" s="15" t="inlineStr">
+      <c r="Q49" s="15" t="inlineStr">
         <is>
           <t>Equity step $</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>InpLotPerStep</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G49" s="11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H49" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I49" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K49" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L49" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M49" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O49" s="11" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P49" s="11" t="inlineStr">
-        <is>
-          <t>لوت لكل خطوة</t>
-        </is>
-      </c>
-      <c r="Q49" s="11" t="inlineStr">
-        <is>
-          <t>Lot per equity step</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>RISK</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>InpMinLot</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
@@ -4582,439 +4582,439 @@
       <c r="D50" s="12" t="n">
         <v>0.01</v>
       </c>
-      <c r="E50" s="15" t="n">
+      <c r="E50" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="F50" s="15" t="n">
+      <c r="F50" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H50" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="H50" s="15" t="n">
+      <c r="I50" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="I50" s="15" t="n">
+      <c r="J50" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="J50" s="15" t="n">
+      <c r="K50" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="K50" s="15" t="n">
+      <c r="L50" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="L50" s="15" t="n">
+      <c r="M50" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M50" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="15" t="n">
+      <c r="O50" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P50" s="11" t="inlineStr">
+        <is>
+          <t>لوت لكل خطوة</t>
+        </is>
+      </c>
+      <c r="Q50" s="11" t="inlineStr">
+        <is>
+          <t>Lot per equity step</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>InpMinLot</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="n">
         <v>0.01</v>
       </c>
-      <c r="O50" s="15" t="inlineStr">
+      <c r="E51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O51" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P50" s="15" t="inlineStr">
+      <c r="P51" s="15" t="inlineStr">
         <is>
           <t>أدنى لوت</t>
         </is>
       </c>
-      <c r="Q50" s="15" t="inlineStr">
+      <c r="Q51" s="15" t="inlineStr">
         <is>
           <t>Minimum lot</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>InpMaxLot</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E52" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="F51" s="11" t="n">
+      <c r="F52" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="11" t="n">
+      <c r="G52" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="11" t="n">
+      <c r="H52" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J51" s="11" t="n">
+      <c r="J52" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="K51" s="11" t="n">
+      <c r="K52" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L51" s="11" t="n">
+      <c r="L52" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="M51" s="11" t="n">
+      <c r="M52" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="N51" s="11" t="n">
+      <c r="N52" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="O51" s="11" t="inlineStr">
+      <c r="O52" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P51" s="11" t="inlineStr">
+      <c r="P52" s="11" t="inlineStr">
         <is>
           <t>أقصى لوت</t>
         </is>
       </c>
-      <c r="Q51" s="11" t="inlineStr">
+      <c r="Q52" s="11" t="inlineStr">
         <is>
           <t>Maximum lot</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>InpMaxPositions</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D52" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="15" t="n">
+      <c r="D53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="15" t="n">
+      <c r="H53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="L52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" s="15" t="n">
+      <c r="L53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="N52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" s="15" t="inlineStr">
+      <c r="N53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P52" s="15" t="inlineStr">
+      <c r="P53" s="15" t="inlineStr">
         <is>
           <t>أقصى عدد صفقات مفتوحة</t>
         </is>
       </c>
-      <c r="Q52" s="15" t="inlineStr">
+      <c r="Q53" s="15" t="inlineStr">
         <is>
           <t>Max open positions</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>InpMaxPerSymbol</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D53" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="11" t="n">
+      <c r="D54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" s="11" t="n">
+      <c r="H54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="N53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="11" t="inlineStr">
+      <c r="N54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P53" s="11" t="inlineStr">
+      <c r="P54" s="11" t="inlineStr">
         <is>
           <t>أقصى صفقات لنفس الرمز</t>
         </is>
       </c>
-      <c r="Q53" s="11" t="inlineStr">
+      <c r="Q54" s="11" t="inlineStr">
         <is>
           <t>Max positions per symbol</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>InpMaxTradesDay</t>
         </is>
       </c>
-      <c r="C54" s="15" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D54" s="12" t="n">
+      <c r="D55" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E54" s="15" t="n">
+      <c r="E55" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F54" s="15" t="n">
+      <c r="F55" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G55" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="H54" s="15" t="n">
+      <c r="H55" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I54" s="15" t="n">
+      <c r="I55" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="J54" s="15" t="n">
+      <c r="J55" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="K54" s="15" t="n">
+      <c r="K55" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="L54" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" s="15" t="n">
+      <c r="L55" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="N54" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" s="15" t="inlineStr">
+      <c r="N55" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P54" s="15" t="inlineStr">
+      <c r="P55" s="15" t="inlineStr">
         <is>
           <t>أقصى صفقات في اليوم</t>
         </is>
       </c>
-      <c r="Q54" s="15" t="inlineStr">
+      <c r="Q55" s="15" t="inlineStr">
         <is>
           <t>Max trades per day</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>InpCooldownBars</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="D56" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="11" t="n">
+      <c r="E56" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F55" s="11" t="n">
+      <c r="F56" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G55" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="11" t="n">
+      <c r="G56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="11" t="n">
+      <c r="I56" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J55" s="11" t="n">
+      <c r="J56" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K55" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="11" t="n">
+      <c r="K56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="N55" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" s="11" t="inlineStr">
+      <c r="N56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P55" s="11" t="inlineStr">
+      <c r="P56" s="11" t="inlineStr">
         <is>
           <t>شموع انتظار بين الدخول</t>
         </is>
       </c>
-      <c r="Q55" s="11" t="inlineStr">
+      <c r="Q56" s="11" t="inlineStr">
         <is>
           <t>Cooldown bars between entries</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>RISK</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>InpLossStreakMax</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>3</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>10</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>إيقاف بعد N خسائر متتالية</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Pause after N consecutive losses</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>InpLossStreakBars</t>
+          <t>InpLossStreakMax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5035,506 +5035,506 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
         <v>4</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
+        <v>10</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>إيقاف بعد N خسائر متتالية</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Pause after N consecutive losses</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>InpLossStreakBars</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>6</v>
+      </c>
+      <c r="I58" t="n">
+        <v>6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>8</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
         <v>30</v>
       </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="inlineStr">
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>طول الإيقاف بالشموع</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Pause length in bars</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>InpMaxDailyLossPct</t>
         </is>
       </c>
-      <c r="C58" s="15" t="inlineStr">
+      <c r="C59" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D58" s="12" t="n">
+      <c r="D59" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E58" s="15" t="n">
+      <c r="E59" s="15" t="n">
         <v>1.5</v>
       </c>
-      <c r="F58" s="15" t="n">
+      <c r="F59" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="15" t="n">
+      <c r="G59" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="H58" s="15" t="n">
+      <c r="H59" s="15" t="n">
         <v>2.5</v>
       </c>
-      <c r="I58" s="15" t="n">
+      <c r="I59" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="J58" s="15" t="n">
+      <c r="J59" s="15" t="n">
         <v>2.5</v>
       </c>
-      <c r="K58" s="15" t="n">
+      <c r="K59" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="L58" s="15" t="n">
+      <c r="L59" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="M58" s="15" t="n">
+      <c r="M59" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="N58" s="15" t="n">
+      <c r="N59" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="O58" s="15" t="inlineStr">
+      <c r="O59" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P58" s="15" t="inlineStr">
+      <c r="P59" s="15" t="inlineStr">
         <is>
           <t>إيقاف يومي عند خسارة %</t>
         </is>
       </c>
-      <c r="Q58" s="15" t="inlineStr">
+      <c r="Q59" s="15" t="inlineStr">
         <is>
           <t>Daily loss halt %</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>InpMaxDrawdownPct</t>
         </is>
       </c>
-      <c r="C59" s="11" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D59" s="12" t="n">
+      <c r="D60" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="E59" s="11" t="n">
+      <c r="E60" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F59" s="11" t="n">
+      <c r="F60" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="G59" s="11" t="n">
+      <c r="G60" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="H59" s="11" t="n">
+      <c r="H60" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="I59" s="11" t="n">
+      <c r="I60" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="J59" s="11" t="n">
+      <c r="J60" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="K59" s="11" t="n">
+      <c r="K60" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="L59" s="11" t="n">
+      <c r="L60" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M59" s="11" t="n">
+      <c r="M60" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N59" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" s="11" t="inlineStr">
+      <c r="N60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P59" s="11" t="inlineStr">
+      <c r="P60" s="11" t="inlineStr">
         <is>
           <t>إيقاف عند ذروة هبوط %</t>
         </is>
       </c>
-      <c r="Q59" s="11" t="inlineStr">
+      <c r="Q60" s="11" t="inlineStr">
         <is>
           <t>Max equity drawdown %</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>InpEmergencyClose</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D60" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" s="15" t="inlineStr">
+      <c r="D61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P60" s="15" t="inlineStr">
+      <c r="P61" s="15" t="inlineStr">
         <is>
           <t>إغلاق كل الصفقات عند خرق الحد</t>
         </is>
       </c>
-      <c r="Q60" s="15" t="inlineStr">
+      <c r="Q61" s="15" t="inlineStr">
         <is>
           <t>Flatten all on risk breach</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>InpAutoSpread</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D61" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" s="11" t="inlineStr">
+      <c r="D62" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P61" s="11" t="inlineStr">
+      <c r="P62" s="11" t="inlineStr">
         <is>
           <t>سقف سبريد تلقائي حسب فئة الأصل</t>
         </is>
       </c>
-      <c r="Q61" s="11" t="inlineStr">
+      <c r="Q62" s="11" t="inlineStr">
         <is>
           <t>Auto spread cap by asset class</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>InpMaxSpreadPoints</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D62" s="12" t="n">
+      <c r="D63" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="E62" s="15" t="n">
+      <c r="E63" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="F62" s="15" t="n">
+      <c r="F63" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="G62" s="15" t="n">
+      <c r="G63" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="H62" s="15" t="n">
+      <c r="H63" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="I62" s="15" t="n">
+      <c r="I63" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="J62" s="15" t="n">
+      <c r="J63" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="K62" s="15" t="n">
+      <c r="K63" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="L62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="15" t="n">
+      <c r="L63" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="N62" s="15" t="n">
+      <c r="N63" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="O62" s="15" t="inlineStr">
+      <c r="O63" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P62" s="15" t="inlineStr">
+      <c r="P63" s="15" t="inlineStr">
         <is>
           <t>أقصى سبريد يدوي بالنقاط</t>
         </is>
       </c>
-      <c r="Q62" s="15" t="inlineStr">
+      <c r="Q63" s="15" t="inlineStr">
         <is>
           <t>Manual max spread in points</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>InpSpreadATRMax</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D63" s="12" t="n">
+      <c r="D64" s="12" t="n">
         <v>0.35</v>
       </c>
-      <c r="E63" s="11" t="n">
+      <c r="E64" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="F63" s="11" t="n">
+      <c r="F64" s="11" t="n">
         <v>0.35</v>
       </c>
-      <c r="G63" s="11" t="n">
+      <c r="G64" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="H63" s="11" t="n">
+      <c r="H64" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="I63" s="11" t="n">
+      <c r="I64" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="J63" s="11" t="n">
+      <c r="J64" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="K63" s="11" t="n">
+      <c r="K64" s="11" t="n">
         <v>0.45</v>
       </c>
-      <c r="L63" s="11" t="n">
+      <c r="L64" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="M63" s="11" t="n">
+      <c r="M64" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="N63" s="11" t="n">
+      <c r="N64" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="O63" s="11" t="inlineStr">
+      <c r="O64" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P63" s="11" t="inlineStr">
+      <c r="P64" s="11" t="inlineStr">
         <is>
           <t>حظر إذا السبريد &gt; ATR ×</t>
         </is>
       </c>
-      <c r="Q63" s="11" t="inlineStr">
+      <c r="Q64" s="11" t="inlineStr">
         <is>
           <t>Block if spread &gt; ATR ×</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>SPREAD</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>InpSpreadStableBars</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" t="n">
-        <v>2</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>5</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>السبريد يجب أن يبقى صالحاً N شموع</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Spread must stay OK for N bars</t>
         </is>
       </c>
     </row>
@@ -5546,2140 +5546,2140 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>InpSpreadStableBars</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>5</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>السبريد يجب أن يبقى صالحاً N شموع</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Spread must stay OK for N bars</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SPREAD</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>InpRolloverPause</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="inlineStr">
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>إيقاف 23:50–00:20 (ليس للكريبتو)</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>Block 23:50–00:20 server (not crypto)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="B66" s="14" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>InpSlippage</t>
         </is>
       </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="C67" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D66" s="12" t="n">
+      <c r="D67" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="15" t="n">
+      <c r="E67" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="F66" s="15" t="n">
+      <c r="F67" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="G66" s="15" t="n">
+      <c r="G67" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="H66" s="15" t="n">
+      <c r="H67" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="I66" s="15" t="n">
+      <c r="I67" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="J66" s="15" t="n">
+      <c r="J67" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="K66" s="15" t="n">
+      <c r="K67" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="L66" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" s="15" t="n">
+      <c r="L67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="N66" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" s="15" t="inlineStr">
+      <c r="N67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P66" s="15" t="inlineStr">
+      <c r="P67" s="15" t="inlineStr">
         <is>
           <t>أقصى انحراف سعر</t>
         </is>
       </c>
-      <c r="Q66" s="15" t="inlineStr">
+      <c r="Q67" s="15" t="inlineStr">
         <is>
           <t>Max price deviation (points)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>InpRetryRequote</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D67" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O67" s="11" t="inlineStr">
+      <c r="D68" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P67" s="11" t="inlineStr">
+      <c r="P68" s="11" t="inlineStr">
         <is>
           <t>إعادة المحاولة عند تغير السعر</t>
         </is>
       </c>
-      <c r="Q67" s="11" t="inlineStr">
+      <c r="Q68" s="11" t="inlineStr">
         <is>
           <t>Retry on requote / price change</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>SPREAD</t>
         </is>
       </c>
-      <c r="B68" s="14" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>InpMaxRetries</t>
         </is>
       </c>
-      <c r="C68" s="15" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D68" s="12" t="n">
+      <c r="D69" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E68" s="15" t="n">
+      <c r="E69" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="15" t="n">
+      <c r="F69" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G68" s="15" t="n">
+      <c r="G69" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="H68" s="15" t="n">
+      <c r="H69" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I68" s="15" t="n">
+      <c r="I69" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="J68" s="15" t="n">
+      <c r="J69" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K68" s="15" t="n">
+      <c r="K69" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="L68" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" s="15" t="n">
+      <c r="L69" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="N68" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O68" s="15" t="inlineStr">
+      <c r="N69" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P68" s="15" t="inlineStr">
+      <c r="P69" s="15" t="inlineStr">
         <is>
           <t>عدد محاولات الإرسال</t>
         </is>
       </c>
-      <c r="Q68" s="15" t="inlineStr">
+      <c r="Q69" s="15" t="inlineStr">
         <is>
           <t>Max send retries</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>InpUseSL</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D69" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" s="11" t="inlineStr">
+      <c r="D70" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P69" s="11" t="inlineStr">
+      <c r="P70" s="11" t="inlineStr">
         <is>
           <t>استخدام وقف الخسارة — لا تعطّله على الحساب الحقيقي</t>
         </is>
       </c>
-      <c r="Q69" s="11" t="inlineStr">
+      <c r="Q70" s="11" t="inlineStr">
         <is>
           <t>Use stop-loss — do not disable on live</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B70" s="14" t="inlineStr">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>InpUseTP</t>
         </is>
       </c>
-      <c r="C70" s="15" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D70" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" s="15" t="inlineStr">
+      <c r="D71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P70" s="15" t="inlineStr">
+      <c r="P71" s="15" t="inlineStr">
         <is>
           <t>استخدام جني الربح</t>
         </is>
       </c>
-      <c r="Q70" s="15" t="inlineStr">
+      <c r="Q71" s="15" t="inlineStr">
         <is>
           <t>Use take-profit</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>InpSLPoints</t>
         </is>
       </c>
-      <c r="C71" s="11" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="11" t="n">
+      <c r="D72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="N71" s="11" t="n">
+      <c r="N72" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O71" s="11" t="inlineStr">
+      <c r="O72" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P71" s="11" t="inlineStr">
+      <c r="P72" s="11" t="inlineStr">
         <is>
           <t>وقف بالنقاط (0 = ATR)</t>
         </is>
       </c>
-      <c r="Q71" s="11" t="inlineStr">
+      <c r="Q72" s="11" t="inlineStr">
         <is>
           <t>SL in points (0 = ATR)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>InpTPPoints</t>
         </is>
       </c>
-      <c r="C72" s="15" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="15" t="n">
+      <c r="D73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="N72" s="15" t="n">
+      <c r="N73" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="O72" s="15" t="inlineStr">
+      <c r="O73" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P72" s="15" t="inlineStr">
+      <c r="P73" s="15" t="inlineStr">
         <is>
           <t>هدف بالنقاط (0 = ATR/RR)</t>
         </is>
       </c>
-      <c r="Q72" s="15" t="inlineStr">
+      <c r="Q73" s="15" t="inlineStr">
         <is>
           <t>TP in points (0 = ATR/RR)</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>InpUseRR</t>
         </is>
       </c>
-      <c r="C73" s="11" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D73" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" s="11" t="inlineStr">
+      <c r="D74" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P73" s="11" t="inlineStr">
+      <c r="P74" s="11" t="inlineStr">
         <is>
           <t>حساب الهدف من نسبة العائد للمخاطرة</t>
         </is>
       </c>
-      <c r="Q73" s="11" t="inlineStr">
+      <c r="Q74" s="11" t="inlineStr">
         <is>
           <t>Take-profit from risk:reward</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>InpRR</t>
         </is>
       </c>
-      <c r="C74" s="15" t="inlineStr">
+      <c r="C75" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D74" s="12" t="n">
+      <c r="D75" s="12" t="n">
         <v>1.6</v>
       </c>
-      <c r="E74" s="15" t="n">
+      <c r="E75" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F74" s="15" t="n">
+      <c r="F75" s="15" t="n">
         <v>1.6</v>
       </c>
-      <c r="G74" s="15" t="n">
+      <c r="G75" s="15" t="n">
         <v>1.2</v>
       </c>
-      <c r="H74" s="15" t="n">
+      <c r="H75" s="15" t="n">
         <v>1.8</v>
       </c>
-      <c r="I74" s="15" t="n">
+      <c r="I75" s="15" t="n">
         <v>1.6</v>
       </c>
-      <c r="J74" s="15" t="n">
+      <c r="J75" s="15" t="n">
         <v>1.8</v>
       </c>
-      <c r="K74" s="15" t="n">
+      <c r="K75" s="15" t="n">
         <v>1.1</v>
       </c>
-      <c r="L74" s="15" t="n">
+      <c r="L75" s="15" t="n">
         <v>0.8</v>
       </c>
-      <c r="M74" s="15" t="n">
+      <c r="M75" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="N74" s="15" t="n">
+      <c r="N75" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="O74" s="15" t="inlineStr">
+      <c r="O75" s="15" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P74" s="15" t="inlineStr">
+      <c r="P75" s="15" t="inlineStr">
         <is>
           <t>العائد : المخاطرة</t>
         </is>
       </c>
-      <c r="Q74" s="15" t="inlineStr">
+      <c r="Q75" s="15" t="inlineStr">
         <is>
           <t>Reward : Risk</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="9" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>InpBreakeven</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D75" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" s="11" t="inlineStr">
+      <c r="D76" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P75" s="11" t="inlineStr">
+      <c r="P76" s="11" t="inlineStr">
         <is>
           <t>نقل الوقف لنقطة التعادل</t>
         </is>
       </c>
-      <c r="Q75" s="11" t="inlineStr">
+      <c r="Q76" s="11" t="inlineStr">
         <is>
           <t>Move stop to breakeven</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="13" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>InpBETriggerPoints</t>
         </is>
       </c>
-      <c r="C76" s="15" t="inlineStr">
+      <c r="C77" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="15" t="n">
+      <c r="D77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="N76" s="15" t="n">
+      <c r="N77" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="O76" s="15" t="inlineStr">
+      <c r="O77" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P76" s="15" t="inlineStr">
+      <c r="P77" s="15" t="inlineStr">
         <is>
           <t>تفعيل التعادل بالنقاط (0=ATR)</t>
         </is>
       </c>
-      <c r="Q76" s="15" t="inlineStr">
+      <c r="Q77" s="15" t="inlineStr">
         <is>
           <t>BE trigger points (0=ATR)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>InpBELockPoints</t>
         </is>
       </c>
-      <c r="C77" s="11" t="inlineStr">
+      <c r="C78" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D77" s="12" t="n">
+      <c r="D78" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E77" s="11" t="n">
+      <c r="E78" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F77" s="11" t="n">
+      <c r="F78" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G77" s="11" t="n">
+      <c r="G78" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="H77" s="11" t="n">
+      <c r="H78" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="I77" s="11" t="n">
+      <c r="I78" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="J77" s="11" t="n">
+      <c r="J78" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="K77" s="11" t="n">
+      <c r="K78" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="L77" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="11" t="n">
+      <c r="L78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="N77" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" s="11" t="inlineStr">
+      <c r="N78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P77" s="11" t="inlineStr">
+      <c r="P78" s="11" t="inlineStr">
         <is>
           <t>قفل ربح عند التعادل بالنقاط</t>
         </is>
       </c>
-      <c r="Q77" s="11" t="inlineStr">
+      <c r="Q78" s="11" t="inlineStr">
         <is>
           <t>Lock profit at BE (points)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="13" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B79" s="14" t="inlineStr">
         <is>
           <t>InpTrailing</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D78" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" s="15" t="inlineStr">
+      <c r="D79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P78" s="15" t="inlineStr">
+      <c r="P79" s="15" t="inlineStr">
         <is>
           <t>وقف متحرك</t>
         </is>
       </c>
-      <c r="Q78" s="15" t="inlineStr">
+      <c r="Q79" s="15" t="inlineStr">
         <is>
           <t>Trailing stop</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>InpTrailStartPoints</t>
         </is>
       </c>
-      <c r="C79" s="11" t="inlineStr">
+      <c r="C80" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="11" t="n">
+      <c r="D80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="11" t="n">
         <v>3000</v>
       </c>
-      <c r="N79" s="11" t="n">
+      <c r="N80" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="O79" s="11" t="inlineStr">
+      <c r="O80" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P79" s="11" t="inlineStr">
+      <c r="P80" s="11" t="inlineStr">
         <is>
           <t>بداية المتحرك بالنقاط (0=ATR)</t>
         </is>
       </c>
-      <c r="Q79" s="11" t="inlineStr">
+      <c r="Q80" s="11" t="inlineStr">
         <is>
           <t>Trail start points (0=ATR)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="13" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B80" s="14" t="inlineStr">
+      <c r="B81" s="14" t="inlineStr">
         <is>
           <t>InpTrailStepPoints</t>
         </is>
       </c>
-      <c r="C80" s="15" t="inlineStr">
+      <c r="C81" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="15" t="n">
+      <c r="D81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="N80" s="15" t="n">
+      <c r="N81" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="O80" s="15" t="inlineStr">
+      <c r="O81" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P80" s="15" t="inlineStr">
+      <c r="P81" s="15" t="inlineStr">
         <is>
           <t>خطوة المتحرك بالنقاط (0=ATR)</t>
         </is>
       </c>
-      <c r="Q80" s="15" t="inlineStr">
+      <c r="Q81" s="15" t="inlineStr">
         <is>
           <t>Trail step points (0=ATR)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>InpPartialClose</t>
         </is>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C82" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D81" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" s="11" t="inlineStr">
+      <c r="D82" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P81" s="11" t="inlineStr">
+      <c r="P82" s="11" t="inlineStr">
         <is>
           <t>إغلاق جزئي</t>
         </is>
       </c>
-      <c r="Q81" s="11" t="inlineStr">
+      <c r="Q82" s="11" t="inlineStr">
         <is>
           <t>Partial close</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B82" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>InpPartialPercent</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr">
+      <c r="C83" s="15" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D82" s="12" t="n">
+      <c r="D83" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="E82" s="15" t="n">
+      <c r="E83" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F82" s="15" t="n">
+      <c r="F83" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="G82" s="15" t="n">
+      <c r="G83" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="H82" s="15" t="n">
+      <c r="H83" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I82" s="15" t="n">
+      <c r="I83" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="J82" s="15" t="n">
+      <c r="J83" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="K82" s="15" t="n">
+      <c r="K83" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="L82" s="15" t="n">
+      <c r="L83" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="M82" s="15" t="n">
+      <c r="M83" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="N82" s="15" t="n">
+      <c r="N83" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="O82" s="15" t="inlineStr">
+      <c r="O83" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P82" s="15" t="inlineStr">
+      <c r="P83" s="15" t="inlineStr">
         <is>
           <t>نسبة الإغلاق الجزئي</t>
         </is>
       </c>
-      <c r="Q82" s="15" t="inlineStr">
+      <c r="Q83" s="15" t="inlineStr">
         <is>
           <t>Partial close percent</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>EXITS</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>InpPartialRR</t>
         </is>
       </c>
-      <c r="C83" s="11" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="D83" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="11" t="n">
+      <c r="D84" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="11" t="n">
         <v>1.2</v>
       </c>
-      <c r="F83" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="11" t="n">
+      <c r="F84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="11" t="n">
         <v>0.8</v>
       </c>
-      <c r="H83" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" s="11" t="n">
+      <c r="H84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="11" t="n">
         <v>0.7</v>
       </c>
-      <c r="L83" s="11" t="n">
+      <c r="L84" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="M83" s="11" t="n">
+      <c r="M84" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="N83" s="11" t="n">
+      <c r="N84" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="O83" s="11" t="inlineStr">
+      <c r="O84" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P83" s="11" t="inlineStr">
+      <c r="P84" s="11" t="inlineStr">
         <is>
           <t>الإغلاق الجزئي عند مضاعف R</t>
         </is>
       </c>
-      <c r="Q83" s="11" t="inlineStr">
+      <c r="Q84" s="11" t="inlineStr">
         <is>
           <t>Partial at R-multiple</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="13" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B84" s="14" t="inlineStr">
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>InpSessionFilter</t>
         </is>
       </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D84" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" s="15" t="inlineStr">
+      <c r="D85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P84" s="15" t="inlineStr">
+      <c r="P85" s="15" t="inlineStr">
         <is>
           <t>فلتر الجلسات (يُعطّل تلقائياً للكريبتو)</t>
         </is>
       </c>
-      <c r="Q84" s="15" t="inlineStr">
+      <c r="Q85" s="15" t="inlineStr">
         <is>
           <t>Session filter (auto-off for crypto)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>InpTradeAsia</t>
         </is>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" s="11" t="inlineStr">
+      <c r="D86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P85" s="11" t="inlineStr">
+      <c r="P86" s="11" t="inlineStr">
         <is>
           <t>جلسة آسيا 00-08</t>
         </is>
       </c>
-      <c r="Q85" s="11" t="inlineStr">
+      <c r="Q86" s="11" t="inlineStr">
         <is>
           <t>Asia session 00-08</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="13" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B86" s="14" t="inlineStr">
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>InpTradeLondon</t>
         </is>
       </c>
-      <c r="C86" s="15" t="inlineStr">
+      <c r="C87" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N86" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" s="15" t="inlineStr">
+      <c r="D87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P86" s="15" t="inlineStr">
+      <c r="P87" s="15" t="inlineStr">
         <is>
           <t>جلسة لندن 08-16</t>
         </is>
       </c>
-      <c r="Q86" s="15" t="inlineStr">
+      <c r="Q87" s="15" t="inlineStr">
         <is>
           <t>London session 08-16</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>InpTradeNewYork</t>
         </is>
       </c>
-      <c r="C87" s="11" t="inlineStr">
+      <c r="C88" s="11" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D87" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" s="11" t="inlineStr">
+      <c r="D88" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P87" s="11" t="inlineStr">
+      <c r="P88" s="11" t="inlineStr">
         <is>
           <t>جلسة نيويورك 13-22</t>
         </is>
       </c>
-      <c r="Q87" s="11" t="inlineStr">
+      <c r="Q88" s="11" t="inlineStr">
         <is>
           <t>New York session 13-22</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="13" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>InpFridayCutoffHour</t>
         </is>
       </c>
-      <c r="C88" s="15" t="inlineStr">
+      <c r="C89" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D88" s="12" t="n">
+      <c r="D89" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E88" s="15" t="n">
+      <c r="E89" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="F88" s="15" t="n">
+      <c r="F89" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="G88" s="15" t="n">
+      <c r="G89" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="H88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="15" t="n">
+      <c r="H89" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="J88" s="15" t="n">
+      <c r="J89" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="K88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="15" t="n">
+      <c r="K89" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="N88" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" s="15" t="inlineStr">
+      <c r="N89" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P88" s="15" t="inlineStr">
+      <c r="P89" s="15" t="inlineStr">
         <is>
           <t>قطع الجمعة (0=إيقاف)</t>
         </is>
       </c>
-      <c r="Q88" s="15" t="inlineStr">
+      <c r="Q89" s="15" t="inlineStr">
         <is>
           <t>Friday cutoff hour (0=off)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>InpMondayDelayHours</t>
         </is>
       </c>
-      <c r="C89" s="11" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D89" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="11" t="n">
+      <c r="D90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F89" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="11" t="n">
+      <c r="F90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N89" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O89" s="11" t="inlineStr">
+      <c r="N90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P89" s="11" t="inlineStr">
+      <c r="P90" s="11" t="inlineStr">
         <is>
           <t>تأخير الاثنين بالساعات</t>
         </is>
       </c>
-      <c r="Q89" s="11" t="inlineStr">
+      <c r="Q90" s="11" t="inlineStr">
         <is>
           <t>Monday delay hours</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="13" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B90" s="14" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>InpServerUtcOffset</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>12</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>فرق السيرفر عن UTC</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Server hours ahead of UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SESSION</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>InpFridayFlatten</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>إغلاق الصفقات قبل عطلة الأسبوع</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Flatten positions before weekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>SESSION</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>InpAvoidNewsWindow</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O90" s="15" t="inlineStr">
+      <c r="D93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P90" s="15" t="inlineStr">
+      <c r="P93" s="15" t="inlineStr">
         <is>
           <t>إيقاف داخل نافذة الأخبار</t>
         </is>
       </c>
-      <c r="Q90" s="15" t="inlineStr">
+      <c r="Q93" s="15" t="inlineStr">
         <is>
           <t>Pause inside news window</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="9" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>InpNewsHourStart</t>
         </is>
       </c>
-      <c r="C91" s="11" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D91" s="12" t="n">
+      <c r="D94" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F94" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="E91" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="F91" s="11" t="n">
+      <c r="G94" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="G91" s="11" t="n">
+      <c r="H94" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="H91" s="11" t="n">
+      <c r="I94" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="I91" s="11" t="n">
+      <c r="J94" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="J91" s="11" t="n">
+      <c r="K94" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="K91" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="L91" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="11" t="n">
+      <c r="L94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="N91" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O91" s="11" t="inlineStr">
+      <c r="N94" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P91" s="11" t="inlineStr">
+      <c r="P94" s="11" t="inlineStr">
         <is>
           <t>بداية نافذة الأخبار</t>
         </is>
       </c>
-      <c r="Q91" s="11" t="inlineStr">
+      <c r="Q94" s="11" t="inlineStr">
         <is>
           <t>News window start hour</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="13" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="13" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B92" s="14" t="inlineStr">
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>InpNewsHourEnd</t>
         </is>
       </c>
-      <c r="C92" s="15" t="inlineStr">
+      <c r="C95" s="15" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D92" s="12" t="n">
+      <c r="D95" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="E92" s="15" t="n">
+      <c r="E95" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="F92" s="15" t="n">
+      <c r="F95" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="G92" s="15" t="n">
+      <c r="G95" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="H92" s="15" t="n">
+      <c r="H95" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="I92" s="15" t="n">
+      <c r="I95" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="J92" s="15" t="n">
+      <c r="J95" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="K92" s="15" t="n">
+      <c r="K95" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="L92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="15" t="n">
+      <c r="L95" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="N92" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O92" s="15" t="inlineStr">
+      <c r="N95" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" s="15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P92" s="15" t="inlineStr">
+      <c r="P95" s="15" t="inlineStr">
         <is>
           <t>نهاية نافذة الأخبار</t>
         </is>
       </c>
-      <c r="Q92" s="15" t="inlineStr">
+      <c r="Q95" s="15" t="inlineStr">
         <is>
           <t>News window end hour</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>SESSION</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>InpMaxHoldBars</t>
         </is>
       </c>
-      <c r="C93" s="11" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="11" t="n">
+      <c r="D96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="F93" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="11" t="n">
+      <c r="F96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="J93" s="11" t="n">
+      <c r="J96" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="K93" s="11" t="n">
+      <c r="K96" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="L93" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="11" t="n">
+      <c r="L96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="N93" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O93" s="11" t="inlineStr">
+      <c r="N96" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P93" s="11" t="inlineStr">
+      <c r="P96" s="11" t="inlineStr">
         <is>
           <t>خروج زمني بعد N شمعة (0=إيقاف)</t>
         </is>
       </c>
-      <c r="Q93" s="11" t="inlineStr">
+      <c r="Q96" s="11" t="inlineStr">
         <is>
           <t>Time exit after N bars (0=off)</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="13" t="inlineStr">
-        <is>
-          <t>ASSET</t>
-        </is>
-      </c>
-      <c r="B94" s="14" t="inlineStr">
-        <is>
-          <t>InpUseAssetProfiles</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="D94" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N94" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O94" s="15" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P94" s="15" t="inlineStr">
-        <is>
-          <t>تكييف الوقف والمخاطرة حسب فئة الأصل</t>
-        </is>
-      </c>
-      <c r="Q94" s="15" t="inlineStr">
-        <is>
-          <t>Adapt SL/risk by asset class</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>ASSET</t>
-        </is>
-      </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>InpCryptoRiskScale</t>
-        </is>
-      </c>
-      <c r="C95" s="11" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D95" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E95" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F95" s="11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G95" s="11" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H95" s="11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I95" s="11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J95" s="11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K95" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L95" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M95" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" s="11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O95" s="11" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SESSION</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>InpMaxHoldHours</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>24</v>
+      </c>
+      <c r="E97" t="n">
+        <v>36</v>
+      </c>
+      <c r="F97" t="n">
+        <v>24</v>
+      </c>
+      <c r="G97" t="n">
+        <v>48</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>24</v>
+      </c>
+      <c r="J97" t="n">
+        <v>36</v>
+      </c>
+      <c r="K97" t="n">
+        <v>8</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>120</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="P95" s="11" t="inlineStr">
-        <is>
-          <t>مضاعف مخاطرة الكريبتو/USDT</t>
-        </is>
-      </c>
-      <c r="Q95" s="11" t="inlineStr">
-        <is>
-          <t>Crypto/USDT risk scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t>ASSET</t>
-        </is>
-      </c>
-      <c r="B96" s="14" t="inlineStr">
-        <is>
-          <t>InpCryptoATRSL</t>
-        </is>
-      </c>
-      <c r="C96" s="15" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D96" s="12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F96" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G96" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I96" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J96" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K96" s="15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L96" s="15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M96" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="N96" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O96" s="15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P96" s="15" t="inlineStr">
-        <is>
-          <t>وقف ATR للكريبتو</t>
-        </is>
-      </c>
-      <c r="Q96" s="15" t="inlineStr">
-        <is>
-          <t>Crypto ATR stop</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>ASSET</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>InpMetalATRSL</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F97" s="11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G97" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H97" s="11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I97" s="11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J97" s="11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K97" s="11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L97" s="11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M97" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N97" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O97" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P97" s="11" t="inlineStr">
-        <is>
-          <t>وقف ATR للمعادن</t>
-        </is>
-      </c>
-      <c r="Q97" s="11" t="inlineStr">
-        <is>
-          <t>Metals ATR stop</t>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>خروج زمني بالساعات (ليس للكريبتو)</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Time-exit hours (skip crypto)</t>
         </is>
       </c>
     </row>
@@ -7691,60 +7691,60 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>InpIndexATRSL</t>
+          <t>InpUseAssetProfiles</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D98" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J98" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L98" s="15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M98" s="15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N98" s="15" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O98" s="15" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P98" s="15" t="inlineStr">
         <is>
-          <t>وقف ATR للمؤشرات</t>
+          <t>تكييف الوقف والمخاطرة حسب فئة الأصل</t>
         </is>
       </c>
       <c r="Q98" s="15" t="inlineStr">
         <is>
-          <t>Indices ATR stop</t>
+          <t>Adapt SL/risk by asset class</t>
         </is>
       </c>
     </row>
@@ -7756,267 +7756,267 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>InpIndexGapFilter</t>
+          <t>InpCryptoRiskScale</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I99" s="11" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J99" s="11" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L99" s="11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M99" s="11" t="n">
         <v>1</v>
       </c>
       <c r="N99" s="11" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="O99" s="11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P99" s="11" t="inlineStr">
         <is>
-          <t>تجاوز فجوة الافتتاح للمؤشرات/الأسهم</t>
+          <t>مضاعف مخاطرة الكريبتو/USDT</t>
         </is>
       </c>
       <c r="Q99" s="11" t="inlineStr">
         <is>
-          <t>Skip opening gap on indices/stocks</t>
+          <t>Crypto/USDT risk scale</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>ASSET</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>InpShowPanel</t>
+          <t>InpCryptoATRSL</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="I100" s="15" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J100" s="15" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="L100" s="15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M100" s="15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N100" s="15" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O100" s="15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P100" s="15" t="inlineStr">
         <is>
-          <t>إظهار لوحة الشارت</t>
+          <t>وقف ATR للكريبتو</t>
         </is>
       </c>
       <c r="Q100" s="15" t="inlineStr">
         <is>
-          <t>Show on-chart HUD</t>
+          <t>Crypto ATR stop</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>ASSET</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>InpPanelX</t>
+          <t>InpMetalATRSL</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>18</v>
+        <v>2.2</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>18</v>
+        <v>2.6</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>18</v>
+        <v>2.2</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v>18</v>
+        <v>1.8</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>18</v>
+        <v>2.2</v>
       </c>
       <c r="I101" s="11" t="n">
-        <v>18</v>
+        <v>2.2</v>
       </c>
       <c r="J101" s="11" t="n">
-        <v>18</v>
+        <v>2.2</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>18</v>
+        <v>1.6</v>
       </c>
       <c r="L101" s="11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M101" s="11" t="n">
-        <v>800</v>
+        <v>5</v>
       </c>
       <c r="N101" s="11" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O101" s="11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P101" s="11" t="inlineStr">
         <is>
-          <t>موضع اللوحة X</t>
+          <t>وقف ATR للمعادن</t>
         </is>
       </c>
       <c r="Q101" s="11" t="inlineStr">
         <is>
-          <t>Panel X</t>
+          <t>Metals ATR stop</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>ASSET</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>InpPanelY</t>
+          <t>InpIndexATRSL</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>double</t>
         </is>
       </c>
       <c r="D102" s="12" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>28</v>
+        <v>2.4</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>28</v>
+        <v>1.6</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="I102" s="15" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J102" s="15" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>28</v>
+        <v>1.5</v>
       </c>
       <c r="L102" s="15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M102" s="15" t="n">
-        <v>800</v>
+        <v>5</v>
       </c>
       <c r="N102" s="15" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O102" s="15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P102" s="15" t="inlineStr">
         <is>
-          <t>موضع اللوحة Y</t>
+          <t>وقف ATR للمؤشرات</t>
         </is>
       </c>
       <c r="Q102" s="15" t="inlineStr">
         <is>
-          <t>Panel Y</t>
+          <t>Indices ATR stop</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>ASSET</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>InpShowTradesOnChart</t>
+          <t>InpIndexGapFilter</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8037,16 +8037,16 @@
         <v>1</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="11" t="n">
         <v>0</v>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="P103" s="11" t="inlineStr">
         <is>
-          <t>رسم الصفقات الحية على الشارت</t>
+          <t>تجاوز فجوة الافتتاح للمؤشرات/الأسهم</t>
         </is>
       </c>
       <c r="Q103" s="11" t="inlineStr">
         <is>
-          <t>Draw live trades on chart</t>
+          <t>Skip opening gap on indices/stocks</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>InpLogToJournal</t>
+          <t>InpShowPanel</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="P104" s="15" t="inlineStr">
         <is>
-          <t>كتابة السجل في Journal</t>
+          <t>إظهار لوحة الشارت</t>
         </is>
       </c>
       <c r="Q104" s="15" t="inlineStr">
         <is>
-          <t>Write journal logs</t>
+          <t>Show on-chart HUD</t>
         </is>
       </c>
     </row>
@@ -8146,58 +8146,318 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
+          <t>InpPanelX</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G105" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H105" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="I105" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="J105" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="K105" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="L105" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="N105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P105" s="11" t="inlineStr">
+        <is>
+          <t>موضع اللوحة X</t>
+        </is>
+      </c>
+      <c r="Q105" s="11" t="inlineStr">
+        <is>
+          <t>Panel X</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>InpPanelY</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F106" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="I106" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="J106" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="K106" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="L106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="N106" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P106" s="15" t="inlineStr">
+        <is>
+          <t>موضع اللوحة Y</t>
+        </is>
+      </c>
+      <c r="Q106" s="15" t="inlineStr">
+        <is>
+          <t>Panel Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>InpShowTradesOnChart</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P107" s="11" t="inlineStr">
+        <is>
+          <t>رسم الصفقات الحية على الشارت</t>
+        </is>
+      </c>
+      <c r="Q107" s="11" t="inlineStr">
+        <is>
+          <t>Draw live trades on chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>InpLogToJournal</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" s="15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P108" s="15" t="inlineStr">
+        <is>
+          <t>كتابة السجل في Journal</t>
+        </is>
+      </c>
+      <c r="Q108" s="15" t="inlineStr">
+        <is>
+          <t>Write journal logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
           <t>InpTimerSec</t>
         </is>
       </c>
-      <c r="C105" s="11" t="inlineStr">
+      <c r="C109" s="11" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D105" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M105" s="11" t="n">
+      <c r="D109" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="N105" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O105" s="11" t="inlineStr">
+      <c r="N109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P105" s="11" t="inlineStr">
+      <c r="P109" s="11" t="inlineStr">
         <is>
           <t>تحديث اللوحة بالثواني</t>
         </is>
       </c>
-      <c r="Q105" s="11" t="inlineStr">
+      <c r="Q109" s="11" t="inlineStr">
         <is>
           <t>HUD refresh seconds</t>
         </is>
@@ -9408,20 +9668,6 @@
           <t>InpLossStreakBars</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>30</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Pause length in bars</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -9703,7 +9949,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
         <is>
@@ -9910,7 +10155,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
